--- a/grupos/3ARHM - Estadisticos 20221.xlsx
+++ b/grupos/3ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="167">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -230,286 +230,286 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AHUET</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOMAN</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>GRANADOS</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>ESPINOSA</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>LETICIA ANETTE</t>
+  </si>
+  <si>
+    <t>ERANDI</t>
+  </si>
+  <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
+    <t>PAZ AIDE</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>ALONDRA VANNESSA</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>NOHEMI</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
     <t>DIEGO ANTONIO</t>
   </si>
   <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>AMY</t>
+  </si>
+  <si>
+    <t>MARIA DEL PILAR</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>CITLALI</t>
+  </si>
+  <si>
+    <t>ALMA PATRICIA</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>NESTOR JOSUE</t>
+  </si>
+  <si>
+    <t>DIANA GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>JARITZA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
     <t>MIXTLI TONATI</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AHUET</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>GRANADOS</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>LETICIA ANETTE</t>
-  </si>
-  <si>
-    <t>ERANDI</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>PAZ AIDE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>AMY</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>ALMA PATRICIA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NESTOR JOSUE</t>
-  </si>
-  <si>
-    <t>DIANA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>JARITZA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
   </si>
   <si>
     <t>MARIELA</t>
@@ -1022,19 +1022,19 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1067,7 +1067,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1099,19 +1099,19 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1176,19 +1176,19 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1253,19 +1253,19 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1298,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1330,19 +1330,19 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1372,13 +1372,13 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1407,19 +1407,19 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1443,19 +1443,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>9</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1484,19 +1484,19 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1529,7 +1529,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1561,19 +1561,19 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1603,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1638,19 +1638,19 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1674,19 +1674,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>10</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1715,19 +1715,19 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1754,10 +1754,10 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1792,19 +1792,19 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1869,19 +1869,19 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1905,16 +1905,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>7</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1946,19 +1946,19 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1985,7 +1985,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -2023,19 +2023,19 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2062,7 +2062,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2100,19 +2100,19 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2148,7 +2148,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2177,19 +2177,19 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2222,10 +2222,10 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2254,19 +2254,19 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2299,7 +2299,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2331,19 +2331,19 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2379,7 +2379,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2408,19 +2408,19 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2450,13 +2450,13 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2467,7 +2467,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -2485,19 +2485,19 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2521,7 +2521,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2533,7 +2533,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2562,19 +2562,19 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2607,7 +2607,7 @@
         <v>5</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2639,19 +2639,19 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2678,13 +2678,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2716,19 +2716,19 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2755,16 +2755,16 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2793,19 +2793,19 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2829,19 +2829,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2870,19 +2870,19 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2906,16 +2906,16 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2947,19 +2947,19 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2983,16 +2983,16 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -3024,19 +3024,19 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3066,7 +3066,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3101,19 +3101,19 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3143,13 +3143,13 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3178,19 +3178,19 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3214,7 +3214,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3223,7 +3223,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3255,19 +3255,19 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3291,13 +3291,13 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3332,19 +3332,19 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3368,7 +3368,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3377,7 +3377,7 @@
         <v>5</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3409,19 +3409,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3448,13 +3448,13 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>8</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3486,19 +3486,19 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3525,7 +3525,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3563,19 +3563,19 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3599,7 +3599,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -3640,19 +3640,19 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3676,7 +3676,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -3699,7 +3699,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -3714,22 +3714,22 @@
         <v>5</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3753,10 +3753,10 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -3768,7 +3768,7 @@
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3794,19 +3794,19 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3830,7 +3830,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U40">
         <v>9</v>
@@ -3839,7 +3839,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3871,19 +3871,19 @@
         <v>9</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3907,7 +3907,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U41">
         <v>10</v>
@@ -3916,7 +3916,7 @@
         <v>6</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -3948,19 +3948,19 @@
         <v>9</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -3984,7 +3984,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U42">
         <v>6</v>
@@ -4064,19 +4064,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>74.36</v>
+        <v>61.54</v>
       </c>
       <c r="G2">
-        <v>25.64</v>
+        <v>38.46</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4096,19 +4096,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="G3">
-        <v>15.38</v>
+        <v>12.82</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>7.69</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -4160,25 +4160,25 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>92.31</v>
+        <v>94.87</v>
       </c>
       <c r="G5">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>5.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4195,27 +4195,27 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>97.44</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -4236,7 +4236,7 @@
         <v>2.56</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4252,7 +4252,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4277,66 +4277,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920237</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920225</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920225</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4372,47 +4312,47 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920225</v>
+        <v>21330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920237</v>
+        <v>21330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920215</v>
+        <v>21330051920033</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
         <v>130</v>
@@ -4423,13 +4363,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920216</v>
+        <v>21330051920217</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
         <v>131</v>
@@ -4440,13 +4380,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920033</v>
+        <v>21330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
         <v>132</v>
@@ -4457,13 +4397,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920217</v>
+        <v>21330051920219</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
@@ -4474,13 +4414,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
         <v>134</v>
@@ -4491,13 +4431,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920219</v>
+        <v>21330051920221</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
         <v>135</v>
@@ -4508,13 +4448,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920220</v>
+        <v>21330051920230</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>136</v>
@@ -4525,13 +4465,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920221</v>
+        <v>21330051920231</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
         <v>137</v>
@@ -4542,13 +4482,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920230</v>
+        <v>21330051920232</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
         <v>138</v>
@@ -4559,13 +4499,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920231</v>
+        <v>21330051920233</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
         <v>139</v>
@@ -4576,13 +4516,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920232</v>
+        <v>21330051920042</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
         <v>140</v>
@@ -4593,13 +4533,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920233</v>
+        <v>21330051920044</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
         <v>141</v>
@@ -4610,13 +4550,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920042</v>
+        <v>21330051920234</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
         <v>142</v>
@@ -4627,13 +4567,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920044</v>
+        <v>21330051920235</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>143</v>
@@ -4644,13 +4584,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920234</v>
+        <v>21330051920236</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>144</v>
@@ -4661,13 +4601,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920235</v>
+        <v>21330051920359</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>145</v>
@@ -4678,13 +4618,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920236</v>
+        <v>21330051920237</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -4695,13 +4635,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920359</v>
+        <v>21330051920239</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -4712,13 +4652,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920239</v>
+        <v>21330051920240</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
@@ -4729,13 +4669,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920240</v>
+        <v>21330051920049</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -4746,13 +4686,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920049</v>
+        <v>21330051920241</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
@@ -4763,13 +4703,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920241</v>
+        <v>21330051920242</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
@@ -4780,13 +4720,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920242</v>
+        <v>21330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -4797,10 +4737,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920244</v>
+        <v>21330051920246</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
         <v>114</v>
@@ -4814,13 +4754,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920246</v>
+        <v>21330051920247</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -4831,13 +4771,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920247</v>
+        <v>21330051920248</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -4848,13 +4788,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920248</v>
+        <v>21330051920249</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -4865,13 +4805,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920249</v>
+        <v>21330051920250</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -4882,13 +4822,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920250</v>
+        <v>21330051920229</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -4899,13 +4839,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920229</v>
+        <v>21330051920228</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -4916,13 +4856,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920228</v>
+        <v>21330051920066</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -4933,13 +4873,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920066</v>
+        <v>21330051920227</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -4950,13 +4890,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920227</v>
+        <v>21330051920226</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -4967,13 +4907,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920226</v>
+        <v>21330051920225</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -4987,10 +4927,10 @@
         <v>21330051920224</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -5004,10 +4944,10 @@
         <v>21330051920223</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
         <v>165</v>
@@ -5021,10 +4961,10 @@
         <v>21330051920222</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
         <v>166</v>
@@ -5040,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5075,13 +5015,13 @@
         <v>21330051920234</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5098,13 +5038,13 @@
         <v>21330051920234</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5118,16 +5058,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5141,16 +5081,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920240</v>
+        <v>21330051920235</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5164,22 +5104,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920219</v>
+        <v>21330051920240</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5187,16 +5127,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920044</v>
+        <v>21330051920240</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
         <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5210,16 +5150,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920250</v>
+        <v>21330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5233,16 +5173,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920222</v>
+        <v>21330051920219</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5251,6 +5191,167 @@
         <v>60</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920220</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920230</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920044</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920239</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920247</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920250</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920222</v>
+      </c>
+      <c r="B16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20221.xlsx
+++ b/grupos/3ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="167">
   <si>
     <t>Materia</t>
   </si>
@@ -1037,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1114,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1150,7 +1150,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1191,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1268,7 +1268,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1422,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1535,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1576,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1653,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1730,7 +1730,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1807,7 +1807,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1884,7 +1884,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1920,7 +1920,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2038,7 +2038,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2115,7 +2115,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2151,7 +2151,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2192,7 +2192,7 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2228,7 +2228,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2269,7 +2269,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2346,7 +2346,7 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2382,7 +2382,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2423,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2459,7 +2459,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2500,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2536,7 +2536,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2577,7 +2577,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2613,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2654,7 +2654,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2731,7 +2731,7 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2808,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2844,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2885,7 +2885,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2962,7 +2962,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3039,7 +3039,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3116,7 +3116,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3193,7 +3193,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3270,7 +3270,7 @@
         <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3347,7 +3347,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3383,7 +3383,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3424,7 +3424,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3537,7 +3537,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3578,7 +3578,7 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3655,7 +3655,7 @@
         <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3732,7 +3732,7 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3768,7 +3768,7 @@
         <v>5</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3809,7 +3809,7 @@
         <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3845,7 +3845,7 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3886,7 +3886,7 @@
         <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3922,7 +3922,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3963,7 +3963,7 @@
         <v>8</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3999,7 +3999,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4204,7 +4204,7 @@
         <v>2.56</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4980,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5012,16 +5012,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5035,16 +5035,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5058,16 +5058,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5081,16 +5081,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5104,22 +5104,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920240</v>
+        <v>21330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5127,16 +5127,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920240</v>
+        <v>21330051920219</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5150,16 +5150,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5173,16 +5173,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920219</v>
+        <v>21330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5196,16 +5196,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920220</v>
+        <v>21330051920044</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5219,16 +5219,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920230</v>
+        <v>21330051920239</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5242,16 +5242,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920044</v>
+        <v>21330051920247</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5265,16 +5265,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920239</v>
+        <v>21330051920250</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -5288,16 +5288,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920247</v>
+        <v>21330051920222</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -5306,52 +5306,6 @@
         <v>60</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920250</v>
-      </c>
-      <c r="B15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920222</v>
-      </c>
-      <c r="B16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>166</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20221.xlsx
+++ b/grupos/3ARHM - Estadisticos 20221.xlsx
@@ -209,13 +209,13 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1040,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1049,10 +1049,10 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1117,7 +1117,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1126,10 +1126,10 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1194,7 +1194,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1203,10 +1203,10 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1271,7 +1271,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1280,10 +1280,10 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1298,7 +1298,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1357,10 +1357,10 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1425,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1434,10 +1434,10 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1502,7 +1502,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1511,10 +1511,10 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1579,7 +1579,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1588,10 +1588,10 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1656,7 +1656,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1665,10 +1665,10 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1733,7 +1733,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1742,10 +1742,10 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1810,7 +1810,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1819,10 +1819,10 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1837,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1887,7 +1887,7 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1896,10 +1896,10 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1964,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1973,10 +1973,10 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2041,7 +2041,7 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2050,10 +2050,10 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2118,7 +2118,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2127,10 +2127,10 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2195,7 +2195,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2204,10 +2204,10 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2272,7 +2272,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2281,10 +2281,10 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2349,7 +2349,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2358,10 +2358,10 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2379,7 +2379,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2426,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2435,10 +2435,10 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2503,7 +2503,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2512,16 +2512,16 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2580,7 +2580,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2589,10 +2589,10 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2657,7 +2657,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2666,10 +2666,10 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2684,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2743,10 +2743,10 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2811,7 +2811,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2820,16 +2820,16 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2838,10 +2838,10 @@
         <v>6</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2888,7 +2888,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2897,10 +2897,10 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2965,7 +2965,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2974,10 +2974,10 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3042,7 +3042,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3051,10 +3051,10 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3119,7 +3119,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3128,10 +3128,10 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3196,7 +3196,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3205,10 +3205,10 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3223,7 +3223,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3273,7 +3273,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3282,10 +3282,10 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3350,7 +3350,7 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3359,10 +3359,10 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3427,7 +3427,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3436,10 +3436,10 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3454,7 +3454,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3504,7 +3504,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3513,10 +3513,10 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3581,7 +3581,7 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3590,10 +3590,10 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3658,7 +3658,7 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3667,10 +3667,10 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3735,7 +3735,7 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3744,10 +3744,10 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3812,7 +3812,7 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -3821,10 +3821,10 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -3839,7 +3839,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3889,7 +3889,7 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -3898,10 +3898,10 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -3916,7 +3916,7 @@
         <v>6</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -3966,7 +3966,7 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -3975,16 +3975,16 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S42">
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U42">
         <v>6</v>
@@ -4128,19 +4128,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>92.31</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G4">
-        <v>7.69</v>
+        <v>10.26</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -4172,7 +4172,7 @@
         <v>5.13</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -4192,19 +4192,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>97.44</v>
+        <v>94.87</v>
       </c>
       <c r="G6">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -4236,7 +4236,7 @@
         <v>2.56</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ARHM - Estadisticos 20221.xlsx
+++ b/grupos/3ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="167">
   <si>
     <t>Materia</t>
   </si>
@@ -203,19 +203,19 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -1043,10 +1043,10 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>8</v>
@@ -1064,7 +1064,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1120,10 +1120,10 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1141,7 +1141,7 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1197,10 +1197,10 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1274,10 +1274,10 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -1351,10 +1351,10 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1428,10 +1428,10 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1449,7 +1449,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1505,10 +1505,10 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -1523,10 +1523,10 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1582,10 +1582,10 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1603,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1659,10 +1659,10 @@
         <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1677,10 +1677,10 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1736,10 +1736,10 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1813,10 +1813,10 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -1890,10 +1890,10 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1967,10 +1967,10 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1988,7 +1988,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -2044,10 +2044,10 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -2121,10 +2121,10 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2139,7 +2139,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2198,10 +2198,10 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>6</v>
@@ -2216,7 +2216,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2275,10 +2275,10 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2352,10 +2352,10 @@
         <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -2370,7 +2370,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2429,10 +2429,10 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2447,10 +2447,10 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2506,10 +2506,10 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -2524,7 +2524,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2583,10 +2583,10 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>7</v>
@@ -2601,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2660,10 +2660,10 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>9</v>
@@ -2681,7 +2681,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2737,10 +2737,10 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2758,7 +2758,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2814,10 +2814,10 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -2832,10 +2832,10 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2891,10 +2891,10 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>9</v>
@@ -2909,10 +2909,10 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2968,10 +2968,10 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>9</v>
@@ -2986,7 +2986,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3045,10 +3045,10 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -3066,7 +3066,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3122,10 +3122,10 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -3140,10 +3140,10 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3199,10 +3199,10 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -3276,10 +3276,10 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3297,7 +3297,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3353,10 +3353,10 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3430,10 +3430,10 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>8</v>
@@ -3507,10 +3507,10 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>9</v>
@@ -3584,10 +3584,10 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -3661,10 +3661,10 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -3738,10 +3738,10 @@
         <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>6</v>
@@ -3815,10 +3815,10 @@
         <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
         <v>9</v>
@@ -3836,7 +3836,7 @@
         <v>9</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3892,10 +3892,10 @@
         <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>9</v>
@@ -3910,7 +3910,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>6</v>
@@ -3969,10 +3969,10 @@
         <v>8</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
         <v>7</v>
@@ -3987,7 +3987,7 @@
         <v>9</v>
       </c>
       <c r="U42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V42">
         <v>5</v>
@@ -4064,19 +4064,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>61.54</v>
+        <v>74.36</v>
       </c>
       <c r="G2">
-        <v>38.46</v>
+        <v>25.64</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4096,19 +4096,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G3">
-        <v>12.82</v>
+        <v>10.26</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -4128,19 +4128,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>89.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="G4">
-        <v>10.26</v>
+        <v>5.13</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -4172,7 +4172,7 @@
         <v>5.13</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -4192,19 +4192,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>94.87</v>
+        <v>97.44</v>
       </c>
       <c r="G6">
-        <v>5.13</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -4236,7 +4236,7 @@
         <v>2.56</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4980,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5012,22 +5012,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920235</v>
+        <v>21330051920234</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5035,22 +5035,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920235</v>
+        <v>21330051920234</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5058,22 +5058,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920240</v>
+        <v>21330051920359</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5081,22 +5081,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920240</v>
+        <v>21330051920359</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5104,16 +5104,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920218</v>
+        <v>21330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920219</v>
+        <v>21330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5150,16 +5150,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920220</v>
+        <v>21330051920044</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5173,16 +5173,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920230</v>
+        <v>21330051920235</v>
       </c>
       <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5196,16 +5196,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920044</v>
+        <v>21330051920240</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5219,16 +5219,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920239</v>
+        <v>21330051920250</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5242,16 +5242,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920247</v>
+        <v>21330051920222</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5260,52 +5260,6 @@
         <v>60</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920250</v>
-      </c>
-      <c r="B13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920222</v>
-      </c>
-      <c r="B14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20221.xlsx
+++ b/grupos/3ARHM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="167">
   <si>
     <t>Materia</t>
   </si>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1132,7 +1132,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1209,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1286,7 +1286,7 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1363,7 +1363,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1440,7 +1440,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1517,7 +1517,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1535,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1594,7 +1594,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1671,7 +1671,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1748,7 +1748,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1825,7 +1825,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1902,7 +1902,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1979,7 +1979,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -2056,7 +2056,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2151,7 +2151,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2210,7 +2210,7 @@
         <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2287,7 +2287,7 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2364,7 +2364,7 @@
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2382,7 +2382,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2441,7 +2441,7 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2518,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2536,7 +2536,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2595,7 +2595,7 @@
         <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2613,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2672,7 +2672,7 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2749,7 +2749,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2826,7 +2826,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2844,7 +2844,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2903,7 +2903,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2980,7 +2980,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -3057,7 +3057,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3134,7 +3134,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3211,7 +3211,7 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3288,7 +3288,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3365,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3442,7 +3442,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3519,7 +3519,7 @@
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3537,7 +3537,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3596,7 +3596,7 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3673,7 +3673,7 @@
         <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3750,7 +3750,7 @@
         <v>5</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -3827,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -3904,7 +3904,7 @@
         <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         <v>8</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -3999,7 +3999,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4204,7 +4204,7 @@
         <v>2.56</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4980,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5012,16 +5012,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920234</v>
+        <v>21330051920359</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5035,22 +5035,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920234</v>
+        <v>21330051920359</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5058,16 +5058,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920359</v>
+        <v>21330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5081,16 +5081,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920359</v>
+        <v>21330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5104,16 +5104,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920237</v>
+        <v>21330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920237</v>
+        <v>21330051920234</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5150,16 +5150,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920044</v>
+        <v>21330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5173,16 +5173,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5196,16 +5196,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920240</v>
+        <v>21330051920250</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5219,16 +5219,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920250</v>
+        <v>21330051920222</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5237,29 +5237,6 @@
         <v>60</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920222</v>
-      </c>
-      <c r="B12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
